--- a/talma_personas.xlsx
+++ b/talma_personas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ADMINISTRACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27158E51-5B46-47DD-A17C-DE0AD7355245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00797887-A61E-434E-8972-99544074B14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E697FF37-14F2-4826-AC93-05468E758264}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="114">
   <si>
     <t>TECNICO AERONAUTICO</t>
   </si>
@@ -341,9 +341,6 @@
     <t>VEGA BLAS JORGE ANTONIO</t>
   </si>
   <si>
-    <t>CODIGO</t>
-  </si>
-  <si>
     <t>RAMPA</t>
   </si>
   <si>
@@ -369,6 +366,21 @@
   </si>
   <si>
     <t>EMAIL</t>
+  </si>
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>MESTANZA HERRERA JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>VISCARRA VELASQUEZ VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>mestanzaherrerajosedaniel@gmail.com</t>
+  </si>
+  <si>
+    <t>torlaxmox.2020.20@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -444,11 +456,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -461,18 +470,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -807,690 +816,690 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D97604D-DB0E-42A4-B509-70A857867E7C}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.08984375" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="9" customWidth="1"/>
     <col min="3" max="3" width="38.453125" customWidth="1"/>
     <col min="4" max="4" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.36328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.90625" customWidth="1"/>
+    <col min="5" max="5" width="19.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="66.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
-        <v>30035535</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="4">
+        <v>71206879</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>30022837</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="4">
+        <v>73939507</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>101</v>
+      <c r="E3" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>30029248</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="4">
+        <v>71317522</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>102</v>
+      <c r="E4" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>30030660</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="4">
+        <v>42405810</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>30035600</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="4">
+        <v>75218608</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>30000224</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="4">
+        <v>40391827</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>103</v>
+      <c r="E7" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>30029867</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="4">
+        <v>71464183</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>30040749</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="4">
+        <v>70518129</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>70021140</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>44331805</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>30029246</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>30000624</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
-        <v>30036066</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A12" s="4">
+        <v>76915727</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
-        <v>30024608</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="4">
+        <v>75263443</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>101</v>
+      <c r="E13" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
-        <v>30028989</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="4">
+        <v>72197757</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
-        <v>30000407</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="A15" s="4">
+        <v>41969953</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>101</v>
+      <c r="E15" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
-        <v>30018115</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="A16" s="4">
+        <v>73349019</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
-        <v>30000147</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="A17" s="4">
+        <v>29698908</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>30008880</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="A18" s="4">
+        <v>47064706</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>103</v>
+      <c r="E18" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>30039751</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="A19" s="4">
+        <v>76738077</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>102</v>
+      <c r="E19" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>30020409</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="A20" s="4">
+        <v>72184638</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>102</v>
+      <c r="E20" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>30039761</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="A21" s="4">
+        <v>73171250</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>101</v>
+      <c r="E21" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>30021457</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="A22" s="4">
+        <v>71761611</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>102</v>
+      <c r="E22" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
-        <v>30037244</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="A23" s="4">
+        <v>71235029</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
-        <v>30012994</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="A24" s="4">
+        <v>74605305</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>30001644</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="A25" s="4">
+        <v>40392481</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>101</v>
+      <c r="E25" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
-        <v>30020941</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="A26" s="4">
+        <v>72462018</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
-        <v>30029242</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="A27" s="4">
+        <v>70320449</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="8" t="s">
-        <v>102</v>
+      <c r="E27" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
-        <v>30040747</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="A28" s="4">
+        <v>71257884</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
-        <v>30040748</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="A29" s="4">
+        <v>71197641</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E29" s="8" t="s">
-        <v>102</v>
+      <c r="E29" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="5">
-        <v>30035604</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="A30" s="4">
+        <v>72761763</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
-        <v>30036062</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="A31" s="4">
+        <v>76452113</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>103</v>
+      <c r="E31" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
-        <v>30035212</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="A32" s="4">
+        <v>72845744</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>101</v>
+      <c r="E32" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="6">
-        <v>30021990</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="A33" s="4">
+        <v>77064550</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>102</v>
+      <c r="E33" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="6">
-        <v>30010139</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="A34" s="4">
+        <v>25775723</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -1498,184 +1507,227 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="5">
-        <v>30029250</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="A35" s="4">
+        <v>73703450</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="6">
-        <v>30041652</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="A36" s="4">
+        <v>71781761</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E36" s="8" t="s">
-        <v>102</v>
+      <c r="E36" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
-        <v>30026011</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="A37" s="4">
+        <v>77694829</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="E37" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
-        <v>30018721</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="A38" s="4">
+        <v>44311871</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="6">
-        <v>30030729</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="A39" s="4">
+        <v>71244335</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>102</v>
+      <c r="E39" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="6">
-        <v>30035529</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="A40" s="4">
+        <v>70799396</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E40" s="8" t="s">
-        <v>102</v>
+      <c r="E40" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="6">
-        <v>30035916</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="A41" s="4">
+        <v>60071505</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>102</v>
+      <c r="E41" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
-        <v>30030658</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="A42" s="4">
+        <v>78013466</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="E42" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
-        <v>30021385</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="A43" s="4">
+        <v>72090130</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="E43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>48214099</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>72908997</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F43" xr:uid="{5D97604D-DB0E-42A4-B509-70A857867E7C}">
@@ -1683,6 +1735,10 @@
       <sortCondition ref="C1:C43"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="F44" r:id="rId1" xr:uid="{69B75650-F018-4A72-B4E4-096840EEE461}"/>
+    <hyperlink ref="F45" r:id="rId2" xr:uid="{E05BE652-F998-407C-B2A3-BB787158E353}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>